--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1893-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1893-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DABA73B-FB06-42E3-9334-1CD109B5E139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4E8D99-5740-48DE-8749-B77D32AD9737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1804,10 +1804,12 @@
         <v>540239</v>
       </c>
       <c r="C5" s="3">
-        <v>33435</v>
+        <f>33435-C8</f>
+        <v>31002</v>
       </c>
       <c r="D5" s="3">
-        <v>24982</v>
+        <f>24982-D8</f>
+        <v>22568</v>
       </c>
       <c r="E5" s="3">
         <v>120209</v>
@@ -1879,29 +1881,29 @@
       </c>
       <c r="AI5" s="43">
         <f>AE5-C5</f>
-        <v>-2433</v>
+        <v>0</v>
       </c>
       <c r="AJ5" s="43">
         <f>AF5-D5</f>
-        <v>-2314</v>
+        <v>100</v>
       </c>
       <c r="AK5" s="42"/>
       <c r="AL5" s="44">
         <f>C5/B5*1000</f>
-        <v>61.889274932020832</v>
+        <v>57.385712619784947</v>
       </c>
       <c r="AM5" s="44">
         <f>D5/B5*1000</f>
-        <v>46.24249637660369</v>
+        <v>41.774103683739973</v>
       </c>
       <c r="AN5" s="42"/>
       <c r="AO5" s="44">
         <f>AL5-K5</f>
-        <v>19.68927493202083</v>
+        <v>15.185712619784944</v>
       </c>
       <c r="AP5" s="44">
         <f>AM5-L5</f>
-        <v>14.842496376603691</v>
+        <v>10.374103683739975</v>
       </c>
     </row>
     <row r="6" spans="1:42">
